--- a/Collections/EURO/Malta/#EURO#Malta#Commemorative#[2009-present]#UNC.xlsx
+++ b/Collections/EURO/Malta/#EURO#Malta#Commemorative#[2009-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Malta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9733CF-2465-4389-B8ED-64437D0719B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F0B96A-20C1-4DE1-9F4D-BCC5BFEE514A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -112,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="112">
   <si>
     <t>Year</t>
   </si>
@@ -440,6 +443,15 @@
   </si>
   <si>
     <t>147.000</t>
+  </si>
+  <si>
+    <t>Pharaoh Hound</t>
+  </si>
+  <si>
+    <t>138.000</t>
+  </si>
+  <si>
+    <t>Valletta</t>
   </si>
 </sst>
 </file>
@@ -771,7 +783,47 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="74">
+  <dxfs count="79">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1370,9 +1422,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="8" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1641,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="11" customWidth="1"/>
@@ -3626,6 +3678,76 @@
         <v/>
       </c>
     </row>
+    <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="8">
+        <v>0</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="9" t="str">
+        <f t="shared" ref="L58" si="14">IF(OR(AND(J58&gt;1,J58&lt;&gt;"-"),AND(K58&gt;1,K58&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="5">
+        <v>2026</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="8">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="9" t="str">
+        <f t="shared" ref="L59" si="15">IF(OR(AND(J59&gt;1,J59&lt;&gt;"-"),AND(K59&gt;1,K59&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:I57" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="4">
@@ -3635,11 +3757,79 @@
     <mergeCell ref="C1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="J3 J5 J7 K3:K7 J9:K10 J12:K12 J19:K19 J21:K21 J24:K24 J26:K26 J29:K29 J31:K31 J33:K33 J35:K35 J39:K39 J14:K15 J17:K17 J37:K37 J36">
-    <cfRule type="containsText" dxfId="73" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="78" priority="205" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5 J3 J7 K3:K7 J9:K10 J12:K12 J19:K19 J21:K21 J24:K24 J26:K26 J29:K29 J31:K31 J33:K33 J35:K35 J39:K39 J14:K15 J17:K17 J37:K37 J36">
+  <conditionalFormatting sqref="J3 J5 J7 K3:K7 J9:K10 J12:K12 J19:K19 J21:K21 J24:K24 J26:K26 J29:K29 J31:K31 J33:K33 J35:K35 J39:K39 J14:K15 J17:K17 J37:K37 J36">
+    <cfRule type="colorScale" priority="206">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="containsText" dxfId="77" priority="197" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="colorScale" priority="198">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6">
+    <cfRule type="containsText" dxfId="76" priority="195" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6">
+    <cfRule type="colorScale" priority="196">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8">
+    <cfRule type="containsText" dxfId="75" priority="193" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8">
+    <cfRule type="colorScale" priority="194">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8">
+    <cfRule type="containsText" dxfId="74" priority="191" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8">
     <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3651,12 +3841,63 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
-    <cfRule type="containsText" dxfId="72" priority="183" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4">
+  <conditionalFormatting sqref="K11">
+    <cfRule type="containsText" dxfId="73" priority="189" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="colorScale" priority="190">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11">
+    <cfRule type="containsText" dxfId="72" priority="187" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11">
+    <cfRule type="colorScale" priority="188">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="containsText" dxfId="71" priority="185" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="colorScale" priority="186">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13">
+    <cfRule type="containsText" dxfId="70" priority="183" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13">
     <cfRule type="colorScale" priority="184">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3668,12 +3909,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6">
-    <cfRule type="containsText" dxfId="71" priority="181" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6">
+  <conditionalFormatting sqref="K18">
+    <cfRule type="containsText" dxfId="69" priority="181" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K18">
     <cfRule type="colorScale" priority="182">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3685,12 +3926,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="70" priority="179" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8">
+  <conditionalFormatting sqref="J18">
+    <cfRule type="containsText" dxfId="68" priority="179" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J18">
     <cfRule type="colorScale" priority="180">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3702,12 +3943,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8">
-    <cfRule type="containsText" dxfId="69" priority="177" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8">
+  <conditionalFormatting sqref="K16">
+    <cfRule type="containsText" dxfId="67" priority="177" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
     <cfRule type="colorScale" priority="178">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3719,12 +3960,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11">
-    <cfRule type="containsText" dxfId="68" priority="175" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11">
+  <conditionalFormatting sqref="J16">
+    <cfRule type="containsText" dxfId="66" priority="175" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16">
     <cfRule type="colorScale" priority="176">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3736,12 +3977,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11">
-    <cfRule type="containsText" dxfId="67" priority="173" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J11">
+  <conditionalFormatting sqref="K20">
+    <cfRule type="containsText" dxfId="65" priority="173" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20">
     <cfRule type="colorScale" priority="174">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3753,12 +3994,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="66" priority="171" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K13">
+  <conditionalFormatting sqref="J20">
+    <cfRule type="containsText" dxfId="64" priority="171" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J20">
     <cfRule type="colorScale" priority="172">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3770,12 +4011,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="65" priority="169" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J13">
+  <conditionalFormatting sqref="K22">
+    <cfRule type="containsText" dxfId="63" priority="169" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K22">
     <cfRule type="colorScale" priority="170">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3787,12 +4028,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K18">
-    <cfRule type="containsText" dxfId="64" priority="167" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K18">
+  <conditionalFormatting sqref="J22">
+    <cfRule type="containsText" dxfId="62" priority="167" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22">
     <cfRule type="colorScale" priority="168">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3804,12 +4045,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J18">
-    <cfRule type="containsText" dxfId="63" priority="165" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J18">
+  <conditionalFormatting sqref="K23">
+    <cfRule type="containsText" dxfId="61" priority="165" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K23">
     <cfRule type="colorScale" priority="166">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3821,12 +4062,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="62" priority="163" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
+  <conditionalFormatting sqref="J23">
+    <cfRule type="containsText" dxfId="60" priority="163" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23">
     <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3838,12 +4079,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="61" priority="161" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J16">
+  <conditionalFormatting sqref="K25">
+    <cfRule type="containsText" dxfId="59" priority="161" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25">
     <cfRule type="colorScale" priority="162">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3855,12 +4096,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K20">
-    <cfRule type="containsText" dxfId="60" priority="159" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K20">
+  <conditionalFormatting sqref="J25">
+    <cfRule type="containsText" dxfId="58" priority="159" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J25">
     <cfRule type="colorScale" priority="160">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3872,12 +4113,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J20">
-    <cfRule type="containsText" dxfId="59" priority="157" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J20">
+  <conditionalFormatting sqref="K27">
+    <cfRule type="containsText" dxfId="57" priority="157" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K27">
     <cfRule type="colorScale" priority="158">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3889,12 +4130,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K22">
-    <cfRule type="containsText" dxfId="58" priority="155" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K22">
+  <conditionalFormatting sqref="J27">
+    <cfRule type="containsText" dxfId="56" priority="155" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J27))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27">
     <cfRule type="colorScale" priority="156">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3906,12 +4147,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J22">
-    <cfRule type="containsText" dxfId="57" priority="153" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J22">
+  <conditionalFormatting sqref="K28">
+    <cfRule type="containsText" dxfId="55" priority="153" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28">
     <cfRule type="colorScale" priority="154">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3923,12 +4164,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K23">
-    <cfRule type="containsText" dxfId="56" priority="151" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K23">
+  <conditionalFormatting sqref="J28">
+    <cfRule type="containsText" dxfId="54" priority="151" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28">
     <cfRule type="colorScale" priority="152">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3940,12 +4181,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J23">
-    <cfRule type="containsText" dxfId="55" priority="149" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J23">
+  <conditionalFormatting sqref="K30">
+    <cfRule type="containsText" dxfId="53" priority="149" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K30">
     <cfRule type="colorScale" priority="150">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3957,12 +4198,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="54" priority="147" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K25">
+  <conditionalFormatting sqref="J30">
+    <cfRule type="containsText" dxfId="52" priority="147" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J30">
     <cfRule type="colorScale" priority="148">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3974,12 +4215,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
-    <cfRule type="containsText" dxfId="53" priority="145" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
+  <conditionalFormatting sqref="K32">
+    <cfRule type="containsText" dxfId="51" priority="145" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K32">
     <cfRule type="colorScale" priority="146">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3991,12 +4232,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K27">
-    <cfRule type="containsText" dxfId="52" priority="143" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K27">
+  <conditionalFormatting sqref="J32">
+    <cfRule type="containsText" dxfId="50" priority="143" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J32">
     <cfRule type="colorScale" priority="144">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4008,12 +4249,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
-    <cfRule type="containsText" dxfId="51" priority="141" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J27))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
+  <conditionalFormatting sqref="K34">
+    <cfRule type="containsText" dxfId="49" priority="141" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34">
     <cfRule type="colorScale" priority="142">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4025,12 +4266,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K28">
-    <cfRule type="containsText" dxfId="50" priority="139" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K28">
+  <conditionalFormatting sqref="J34">
+    <cfRule type="containsText" dxfId="48" priority="139" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J34">
     <cfRule type="colorScale" priority="140">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4042,12 +4283,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
-    <cfRule type="containsText" dxfId="49" priority="137" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
+  <conditionalFormatting sqref="J38:K38">
+    <cfRule type="containsText" dxfId="47" priority="137" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J38))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J38:K38">
     <cfRule type="colorScale" priority="138">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4059,46 +4300,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K30">
-    <cfRule type="containsText" dxfId="48" priority="135" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K30">
-    <cfRule type="colorScale" priority="136">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J30">
-    <cfRule type="containsText" dxfId="47" priority="133" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J30">
-    <cfRule type="colorScale" priority="134">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K32">
+  <conditionalFormatting sqref="J40">
     <cfRule type="containsText" dxfId="46" priority="131" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K32">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J40))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J40">
     <cfRule type="colorScale" priority="132">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4110,12 +4317,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J32">
+  <conditionalFormatting sqref="K40">
     <cfRule type="containsText" dxfId="45" priority="129" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J32">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K40))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K40">
     <cfRule type="colorScale" priority="130">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4127,12 +4334,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K34">
+  <conditionalFormatting sqref="J43">
     <cfRule type="containsText" dxfId="44" priority="127" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J43))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J43">
     <cfRule type="colorScale" priority="128">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4144,12 +4351,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J34">
+  <conditionalFormatting sqref="K43">
     <cfRule type="containsText" dxfId="43" priority="125" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J34">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K43))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K43">
     <cfRule type="colorScale" priority="126">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4161,12 +4368,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J38:K38">
+  <conditionalFormatting sqref="J41">
     <cfRule type="containsText" dxfId="42" priority="123" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J38))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J38:K38">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J41))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41">
     <cfRule type="colorScale" priority="124">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4178,29 +4385,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J40">
-    <cfRule type="containsText" dxfId="41" priority="117" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J40))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J40">
-    <cfRule type="colorScale" priority="118">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K40">
+  <conditionalFormatting sqref="J42">
+    <cfRule type="containsText" dxfId="41" priority="119" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J42))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J42">
+    <cfRule type="colorScale" priority="120">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K41">
     <cfRule type="containsText" dxfId="40" priority="115" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K40))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K40">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K41))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K41">
     <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4212,12 +4419,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J43">
+  <conditionalFormatting sqref="K42">
     <cfRule type="containsText" dxfId="39" priority="113" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J43">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K42))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K42">
     <cfRule type="colorScale" priority="114">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4229,12 +4436,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K43">
+  <conditionalFormatting sqref="J44">
     <cfRule type="containsText" dxfId="38" priority="111" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K43))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K43">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J44))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J44">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4246,46 +4453,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41">
-    <cfRule type="containsText" dxfId="37" priority="109" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J41))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J41">
-    <cfRule type="colorScale" priority="110">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J42">
-    <cfRule type="containsText" dxfId="36" priority="105" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J42))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J42">
-    <cfRule type="colorScale" priority="106">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
+  <conditionalFormatting sqref="K44">
+    <cfRule type="containsText" dxfId="37" priority="107" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K44))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K44">
+    <cfRule type="colorScale" priority="108">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45">
+    <cfRule type="containsText" dxfId="36" priority="103" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K45))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45">
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J46">
     <cfRule type="containsText" dxfId="35" priority="101" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K41))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J46))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J46">
     <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4297,29 +4504,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K42">
-    <cfRule type="containsText" dxfId="34" priority="99" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K42))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K42">
-    <cfRule type="colorScale" priority="100">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J44">
-    <cfRule type="containsText" dxfId="33" priority="97" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J44))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J44">
+  <conditionalFormatting sqref="J47">
+    <cfRule type="containsText" dxfId="34" priority="97" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J47))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J47">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4331,12 +4521,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
+  <conditionalFormatting sqref="K47">
+    <cfRule type="containsText" dxfId="33" priority="95" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K47))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K47">
+    <cfRule type="colorScale" priority="96">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48">
     <cfRule type="containsText" dxfId="32" priority="93" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K44))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J48))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48">
     <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4348,12 +4555,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
-    <cfRule type="containsText" dxfId="31" priority="89" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K45))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
+  <conditionalFormatting sqref="K48">
+    <cfRule type="containsText" dxfId="31" priority="91" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K48))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K48">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K46">
+    <cfRule type="containsText" dxfId="30" priority="89" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K46))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K46">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4365,97 +4589,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J46">
-    <cfRule type="containsText" dxfId="30" priority="87" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J46))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J46">
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J47">
-    <cfRule type="containsText" dxfId="29" priority="83" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J47))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J47">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K47">
-    <cfRule type="containsText" dxfId="28" priority="81" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K47))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K47">
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J48">
-    <cfRule type="containsText" dxfId="27" priority="79" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J48))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J48">
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K48">
-    <cfRule type="containsText" dxfId="26" priority="77" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K48))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K48">
-    <cfRule type="colorScale" priority="78">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K46">
-    <cfRule type="containsText" dxfId="25" priority="75" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K46))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K46">
+  <conditionalFormatting sqref="K51">
+    <cfRule type="containsText" dxfId="29" priority="75" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K51))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K51">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4467,12 +4606,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K51">
-    <cfRule type="containsText" dxfId="24" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K51))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K51">
+  <conditionalFormatting sqref="K53">
+    <cfRule type="containsText" dxfId="28" priority="67" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K53))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K53">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J49">
+    <cfRule type="containsText" dxfId="27" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J49))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J49">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J50">
+    <cfRule type="containsText" dxfId="26" priority="61" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J50))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J50">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4484,12 +4657,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K53">
-    <cfRule type="containsText" dxfId="23" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K53))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K53">
+  <conditionalFormatting sqref="K49">
+    <cfRule type="containsText" dxfId="25" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K49))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K49">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K50">
+    <cfRule type="containsText" dxfId="24" priority="53" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K50))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K50">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4501,29 +4691,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J49">
-    <cfRule type="containsText" dxfId="22" priority="49" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J49))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J49">
-    <cfRule type="colorScale" priority="50">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J50">
-    <cfRule type="containsText" dxfId="21" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J50))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J50">
+  <conditionalFormatting sqref="K52">
+    <cfRule type="containsText" dxfId="23" priority="51" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K52))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K52">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K36">
+    <cfRule type="containsText" dxfId="22" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K36">
     <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4535,12 +4725,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K49">
-    <cfRule type="containsText" dxfId="20" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K49))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K49">
+  <conditionalFormatting sqref="J51">
+    <cfRule type="containsText" dxfId="21" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J51))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J51">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J52">
+    <cfRule type="containsText" dxfId="20" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J52))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J52">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J53">
+    <cfRule type="containsText" dxfId="19" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J53))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J53">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4552,12 +4776,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K50">
-    <cfRule type="containsText" dxfId="19" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K50))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K50">
+  <conditionalFormatting sqref="J45">
+    <cfRule type="containsText" dxfId="18" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J45))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J45">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4569,46 +4793,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K52">
-    <cfRule type="containsText" dxfId="18" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K52))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K52">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K36">
-    <cfRule type="containsText" dxfId="17" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K36))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K36">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J51">
+  <conditionalFormatting sqref="K54">
+    <cfRule type="containsText" dxfId="17" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K54))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K54">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K55">
     <cfRule type="containsText" dxfId="16" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J51))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J51">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K55))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K55">
     <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4620,12 +4827,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J52">
+  <conditionalFormatting sqref="J54">
     <cfRule type="containsText" dxfId="15" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J52))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J52">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J54))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J54">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4637,12 +4844,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J53">
+  <conditionalFormatting sqref="J55">
     <cfRule type="containsText" dxfId="14" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J53))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J53">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J55))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J55">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4654,12 +4861,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J45">
+  <conditionalFormatting sqref="K56">
     <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J45))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J45">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K56))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K56">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4671,29 +4878,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K54">
-    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K54))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K54">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K55">
+  <conditionalFormatting sqref="K57">
+    <cfRule type="containsText" dxfId="12" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K57))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K57">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J56">
     <cfRule type="containsText" dxfId="11" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K55))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K55">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J56))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J56">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4705,12 +4912,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J54">
+  <conditionalFormatting sqref="J57">
     <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J54))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J54">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J57))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J57">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4722,12 +4929,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J55">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J55))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J55">
+  <conditionalFormatting sqref="K58">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K58))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K58">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4739,29 +4946,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K56))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K56">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K57">
-    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K57))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K57">
+  <conditionalFormatting sqref="J58">
+    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J58))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J58">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4773,12 +4963,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J56">
+  <conditionalFormatting sqref="K59">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J56))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J56">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K59))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K59">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4790,12 +4980,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J57">
+  <conditionalFormatting sqref="J59">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(J57))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J57">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(J59))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J59">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>

--- a/Collections/EURO/Malta/#EURO#Malta#Commemorative#[2009-present]#UNC.xlsx
+++ b/Collections/EURO/Malta/#EURO#Malta#Commemorative#[2009-present]#UNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Malta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F0B96A-20C1-4DE1-9F4D-BCC5BFEE514A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F65857-E0E4-4E20-B8AA-7D4038BBCB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -783,63 +783,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="79">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="76">
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -848,6 +792,38 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1422,9 +1398,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="8" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3757,11 +3733,11 @@
     <mergeCell ref="C1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="J3 J5 J7 K3:K7 J9:K10 J12:K12 J19:K19 J21:K21 J24:K24 J26:K26 J29:K29 J31:K31 J33:K33 J35:K35 J39:K39 J14:K15 J17:K17 J37:K37 J36">
-    <cfRule type="containsText" dxfId="78" priority="205" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="75" priority="205" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3 J5 J7 K3:K7 J9:K10 J12:K12 J19:K19 J21:K21 J24:K24 J26:K26 J29:K29 J31:K31 J33:K33 J35:K35 J39:K39 J14:K15 J17:K17 J37:K37 J36">
+  <conditionalFormatting sqref="J5 J3 J7 K3:K7 J9:K10 J12:K12 J19:K19 J21:K21 J24:K24 J26:K26 J29:K29 J31:K31 J33:K33 J35:K35 J39:K39 J14:K15 J17:K17 J37:K37 J36">
     <cfRule type="colorScale" priority="206">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3774,7 +3750,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4">
-    <cfRule type="containsText" dxfId="77" priority="197" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="74" priority="197" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3791,7 +3767,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6">
-    <cfRule type="containsText" dxfId="76" priority="195" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="73" priority="195" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3808,7 +3784,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8">
-    <cfRule type="containsText" dxfId="75" priority="193" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="72" priority="193" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3825,7 +3801,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8">
-    <cfRule type="containsText" dxfId="74" priority="191" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="71" priority="191" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J8))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3842,7 +3818,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="containsText" dxfId="73" priority="189" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="70" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K11))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3859,7 +3835,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11">
-    <cfRule type="containsText" dxfId="72" priority="187" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="69" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J11))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3876,7 +3852,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="containsText" dxfId="71" priority="185" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="68" priority="185" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3893,7 +3869,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J13">
-    <cfRule type="containsText" dxfId="70" priority="183" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="67" priority="183" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J13))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3910,7 +3886,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18">
-    <cfRule type="containsText" dxfId="69" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="66" priority="181" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3927,7 +3903,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J18">
-    <cfRule type="containsText" dxfId="68" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="65" priority="179" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J18))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3944,7 +3920,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="containsText" dxfId="67" priority="177" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="64" priority="177" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3961,7 +3937,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J16">
-    <cfRule type="containsText" dxfId="66" priority="175" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="63" priority="175" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J16))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3978,7 +3954,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K20">
-    <cfRule type="containsText" dxfId="65" priority="173" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="62" priority="173" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K20))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3995,7 +3971,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J20">
-    <cfRule type="containsText" dxfId="64" priority="171" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="61" priority="171" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J20))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4012,7 +3988,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22">
-    <cfRule type="containsText" dxfId="63" priority="169" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="60" priority="169" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4029,7 +4005,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J22">
-    <cfRule type="containsText" dxfId="62" priority="167" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="59" priority="167" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J22))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4046,7 +4022,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K23">
-    <cfRule type="containsText" dxfId="61" priority="165" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="58" priority="165" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4063,7 +4039,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23">
-    <cfRule type="containsText" dxfId="60" priority="163" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="57" priority="163" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J23))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4080,7 +4056,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="containsText" dxfId="59" priority="161" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="56" priority="161" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4097,7 +4073,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25">
-    <cfRule type="containsText" dxfId="58" priority="159" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="55" priority="159" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J25))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4114,7 +4090,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="containsText" dxfId="57" priority="157" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="54" priority="157" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4131,7 +4107,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27">
-    <cfRule type="containsText" dxfId="56" priority="155" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="53" priority="155" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J27))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4148,7 +4124,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K28">
-    <cfRule type="containsText" dxfId="55" priority="153" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="52" priority="153" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4165,7 +4141,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J28">
-    <cfRule type="containsText" dxfId="54" priority="151" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="51" priority="151" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J28))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4182,7 +4158,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="containsText" dxfId="53" priority="149" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="50" priority="149" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4199,7 +4175,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J30">
-    <cfRule type="containsText" dxfId="52" priority="147" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="49" priority="147" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J30))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4216,7 +4192,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K32">
-    <cfRule type="containsText" dxfId="51" priority="145" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="48" priority="145" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4233,7 +4209,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
-    <cfRule type="containsText" dxfId="50" priority="143" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="47" priority="143" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J32))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4250,7 +4226,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K34">
-    <cfRule type="containsText" dxfId="49" priority="141" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="46" priority="141" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4267,7 +4243,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J34">
-    <cfRule type="containsText" dxfId="48" priority="139" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="139" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J34))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4284,7 +4260,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J38:K38">
-    <cfRule type="containsText" dxfId="47" priority="137" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="137" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J38))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4301,7 +4277,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J40">
-    <cfRule type="containsText" dxfId="46" priority="131" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="43" priority="131" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J40))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4318,7 +4294,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="containsText" dxfId="45" priority="129" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="129" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K40))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4335,7 +4311,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J43">
-    <cfRule type="containsText" dxfId="44" priority="127" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="41" priority="127" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J43))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4352,7 +4328,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K43">
-    <cfRule type="containsText" dxfId="43" priority="125" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="40" priority="125" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K43))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4369,7 +4345,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41">
-    <cfRule type="containsText" dxfId="42" priority="123" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="123" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J41))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4386,7 +4362,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J42">
-    <cfRule type="containsText" dxfId="41" priority="119" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="119" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J42))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4403,7 +4379,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="containsText" dxfId="40" priority="115" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="115" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K41))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4420,7 +4396,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="containsText" dxfId="39" priority="113" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="113" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K42))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4437,7 +4413,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J44">
-    <cfRule type="containsText" dxfId="38" priority="111" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="111" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J44))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4454,7 +4430,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K44">
-    <cfRule type="containsText" dxfId="37" priority="107" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="107" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K44))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4471,7 +4447,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K45">
-    <cfRule type="containsText" dxfId="36" priority="103" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="103" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K45))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4488,7 +4464,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J46">
-    <cfRule type="containsText" dxfId="35" priority="101" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="101" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J46))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4505,7 +4481,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J47">
-    <cfRule type="containsText" dxfId="34" priority="97" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="97" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J47))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4522,7 +4498,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K47">
-    <cfRule type="containsText" dxfId="33" priority="95" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="95" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K47))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4539,7 +4515,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J48">
-    <cfRule type="containsText" dxfId="32" priority="93" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="93" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J48))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4556,7 +4532,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K48">
-    <cfRule type="containsText" dxfId="31" priority="91" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="91" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K48))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4573,7 +4549,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K46">
-    <cfRule type="containsText" dxfId="30" priority="89" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="89" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K46))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4590,7 +4566,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K51">
-    <cfRule type="containsText" dxfId="29" priority="75" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="75" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K51))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4607,7 +4583,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K53">
-    <cfRule type="containsText" dxfId="28" priority="67" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K53))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4624,7 +4600,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J49">
-    <cfRule type="containsText" dxfId="27" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="63" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J49))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4641,7 +4617,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J50">
-    <cfRule type="containsText" dxfId="26" priority="61" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="61" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J50))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4658,7 +4634,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K49">
-    <cfRule type="containsText" dxfId="25" priority="55" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="55" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K49))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4675,7 +4651,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K50">
-    <cfRule type="containsText" dxfId="24" priority="53" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="53" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K50))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4692,7 +4668,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K52">
-    <cfRule type="containsText" dxfId="23" priority="51" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K52))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4709,7 +4685,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K36">
-    <cfRule type="containsText" dxfId="22" priority="47" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K36))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4726,7 +4702,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J51">
-    <cfRule type="containsText" dxfId="21" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="45" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J51))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4743,7 +4719,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J52">
-    <cfRule type="containsText" dxfId="20" priority="43" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J52))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4760,7 +4736,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J53">
-    <cfRule type="containsText" dxfId="19" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J53))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4777,7 +4753,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J45">
-    <cfRule type="containsText" dxfId="18" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J45))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4794,7 +4770,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K54">
-    <cfRule type="containsText" dxfId="17" priority="35" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="35" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4811,7 +4787,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K55">
-    <cfRule type="containsText" dxfId="16" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K55))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4828,7 +4804,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J54">
-    <cfRule type="containsText" dxfId="15" priority="29" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="29" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J54))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4845,7 +4821,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J55">
-    <cfRule type="containsText" dxfId="14" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J55))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4862,7 +4838,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K56))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4879,7 +4855,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K57">
-    <cfRule type="containsText" dxfId="12" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K57))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4896,7 +4872,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J56">
-    <cfRule type="containsText" dxfId="11" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J56))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4913,7 +4889,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J57">
-    <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J57))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4947,7 +4923,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J58">
-    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J58))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4964,7 +4940,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K59">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K59))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4981,7 +4957,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J59">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(J59))))</formula>
     </cfRule>
   </conditionalFormatting>
